--- a/backend/data/submissions.xlsx
+++ b/backend/data/submissions.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -925,6 +925,57 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>Excellent service</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-11T15:51:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Mercy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mercy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Excellent effort: It is clear to see that you put in your absolute best and this is a sign you’ll achieve great success in your life in the future.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-11T16:03:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mercy</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mercy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DELETE FROM employees
+WHERE id IN (1, 2, 3, 4, 5, 6, 7);</t>
         </is>
       </c>
     </row>
@@ -939,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -996,6 +1047,33 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-11T15:56:36</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Debug User</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>debug@example.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Web Development</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DB test from codex</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/data/submissions.xlsx
+++ b/backend/data/submissions.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2620" yWindow="2620" windowWidth="14400" windowHeight="7270" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="careers" sheetId="1" state="visible" r:id="rId1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="21.453125" customWidth="1" min="5" max="5"/>
@@ -784,9 +784,106 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-14T15:43:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>krish</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>krish@gmail.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Frontend Developer</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:8000/resumes/resume_sethu_78cc2bb6ea664ff39f8831d1f1d4519c.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-14T16:00:21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>emillian</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>emillians@gmail.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8907654321</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Digital Marketing Executive</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:8000/resumes/sethu_resume_pdf_11ff48b2a3ee436eb17de74157b8d96f.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-14T16:04:16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mercy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mercy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8907654321</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Digital Marketing Executive</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:8000/resumes/sethu_resume_pdf_94c2a206379b4eeb90af313c2ce1116d.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
